--- a/artfynd/A 42489-2025 artfynd.xlsx
+++ b/artfynd/A 42489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93561652</v>
+        <v>67229545</v>
       </c>
       <c r="B2" t="n">
-        <v>90663</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,27 @@
           <t>(Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>bässe, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599731.2681490124</v>
+        <v>599747</v>
       </c>
       <c r="R2" t="n">
-        <v>6820319.823886042</v>
+        <v>6820337</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,27 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Fjolårsex</t>
+          <t>På samma plats som tidigere år, tillsammans med S.lundellii</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,68 +773,84 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog i branter</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Örtrik granskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>marken</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93561698</v>
+        <v>62130461</v>
       </c>
       <c r="B3" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2058</v>
+        <v>789</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599729.138830675</v>
+        <v>599727</v>
       </c>
       <c r="R3" t="n">
-        <v>6820310.686862195</v>
+        <v>6820329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,27 +877,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjolårsex</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,68 +891,59 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>gammal granskog i bäckmiljö på sandmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95540382</v>
+        <v>93561652</v>
       </c>
       <c r="B4" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2058</v>
+        <v>789</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -968,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599730.2297891579</v>
+        <v>599731</v>
       </c>
       <c r="R4" t="n">
-        <v>6820322.660067433</v>
+        <v>6820320</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,27 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Återfynd tillsammans med raggtaggsvamp</t>
+          <t>Fjolårsex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,50 +1005,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Rikare barrblandskog vid bäckravin</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Marken</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Marken</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95540358</v>
+        <v>95488219</v>
       </c>
       <c r="B5" t="n">
-        <v>90663</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,16 +1048,8 @@
           <t>(Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1117,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599730.2297891579</v>
+        <v>599727</v>
       </c>
       <c r="R5" t="n">
-        <v>6820322.660067433</v>
+        <v>6820334</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,27 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Återfynd på samma lokal tillsammans med koppartaggsvamp</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,33 +1106,1728 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Rikare barrblandskog vid bäckravin</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Marken</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Max Rosendahl, Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95502182</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93207</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>789</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum mirabile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bässe, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>599732</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6820331</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Max Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Max Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95540358</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93207</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>789</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum mirabile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599730</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6820323</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Återfynd på samma lokal tillsammans med koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Rikare barrblandskog vid bäckravin</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Marken</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127755802</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93207</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>789</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum mirabile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bässe vid bäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>599782</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6820318</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Återfynd lokalen vid bäcken</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>93561579</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599758</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6820312</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Låga</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>93961538</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599751</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6820328</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-06-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6928476</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93205</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>bässe, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599747</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6820337</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-08-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-08-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik bäckravin</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>93561698</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93205</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>599729</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6820311</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fjolårsex</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95488200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93205</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>599727</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6820334</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Max Rosendahl, Andreas Thomas Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95540382</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93205</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599730</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6820323</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Återfynd tillsammans med raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Rikare barrblandskog vid bäckravin</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Marken</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Marken</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128316972</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93205</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bässe vid bäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>599782</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6820318</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Återfynd 4 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>85678930</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92281</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>bässe, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>599747</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6820337</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Två små fruktkroppar och flera på gång, strax efter där raggtaggsvampen växer</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrblandskog i bäckravin med lågor och död ved</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Substratet ullticka på granlåga.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119358810</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93193</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>bässe, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>599747</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6820337</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Växte i en liten grupp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>62130463</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>599744</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6820322</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>gammal granskog i bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128317134</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89138</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4404</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sotvaxskivling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hygrophorus camarophyllus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bässe vid bäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>599782</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6820318</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad barrblandskog främst gran med inslag av äldre tall och björk</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alf Bjarne Roland Pallin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>62130462</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>599726</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6820332</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>gammal granskog i bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
